--- a/AAII_Financials/Quarterly/TLGPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TLGPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>TLGPY</t>
   </si>
@@ -656,99 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -791,23 +799,29 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>7318600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>7597300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8048900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>8385700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8328200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -850,23 +864,29 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>2803800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2951100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3058400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3147000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2899600</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -909,23 +929,29 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>4514800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4646100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4990500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>5238700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5428600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +973,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1034,14 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1099,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1109,23 +1149,29 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>97300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>356000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>125700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>859500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1168,23 +1214,29 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
         <v>1618400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1721300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1801100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1416700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1416700</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,8 +1255,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1247,23 +1301,29 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>6842200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7382100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7518200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>8220300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1306,23 +1366,29 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>476400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>215200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>530700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>165400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>598800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1410,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1388,23 +1456,29 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>603700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>743500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>838400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>900600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>822500</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1447,23 +1521,29 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>2698500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>889000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3170200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1066000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2838000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1506,23 +1586,29 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>191200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>221700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>260000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>222300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1565,23 +1651,29 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>888800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>737000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1109000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>843700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1189100</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1624,23 +1716,29 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>139300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>283600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>348100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>234200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,8 +1796,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1742,23 +1846,29 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>749600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>453400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>761000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>609400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>812600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1801,23 +1911,29 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>731600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>447400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>753700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>609400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>815900</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1991,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1919,23 +2041,29 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2121,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2186,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2096,23 +2236,29 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-603700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-743500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-838400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-900600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-822500</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2155,23 +2301,29 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>731600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>447400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>753700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>609400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>815900</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,8 +2381,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2273,87 +2431,99 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>731600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>447400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>753700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>609400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>815900</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2545,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,112 +2570,120 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>763100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>757000</v>
+      </c>
+      <c r="F41" s="3">
         <v>957800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>949800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>663500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>631200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>634300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>710700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>697900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>682100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>692600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>655600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>620300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>625000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>708200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>862900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>328300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>498900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>399700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>358000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>51200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>50800</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>3300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>18000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>17600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>15300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>15400</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2516,421 +2696,469 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2414400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2395200</v>
+      </c>
+      <c r="F43" s="3">
         <v>2203200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2184700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2572000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2446700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2458700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2754600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2577400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2519100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2970000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2811500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2907200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2929000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2791400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3061000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3370900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3509700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3572500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3624800</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>356300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>353400</v>
+      </c>
+      <c r="F44" s="3">
         <v>383500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>380300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>318000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>302500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>402900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>451400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>345600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>337800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>467600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>442700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>363400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>366100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>494800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>307200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>275000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>493000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>296400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>575000</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>411600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>408400</v>
+      </c>
+      <c r="F45" s="3">
         <v>531600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>527200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>474000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>450900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>598400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>670500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>230200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>225000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>133600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>126500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>356700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>359400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>334400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>689600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>325100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>444000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>563800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>365900</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4280200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4246200</v>
+      </c>
+      <c r="F46" s="3">
         <v>4294300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4258200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4258200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4050800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4300400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4818000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4074600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3982400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4472400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4233700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4481200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4514900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4526600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4920600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4299400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4945500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4832400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4923700</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>441400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>437900</v>
+      </c>
+      <c r="F47" s="3">
         <v>417600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>414000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>395300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>376100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>157200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>176100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>446400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>436300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>468300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>443300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>471200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>474800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>525400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1546500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1543700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1675400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1391600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1430600</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16161900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>16033500</v>
+      </c>
+      <c r="F48" s="3">
         <v>15456900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>15327100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>15296700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14551600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>14417400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16152700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>15701200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>15345900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>16135000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>15273900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>15836300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15955200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>16125900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>15960600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>16140100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>16477700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>14777100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14940500</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7499800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7440300</v>
+      </c>
+      <c r="F49" s="3">
         <v>7524000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7460800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7719800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7343800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7612500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8528700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8287300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8099800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8023200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>7595000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7313800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>7368700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7330300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4739400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4877100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4762300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>4770900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5176500</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3216,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3281,79 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>515400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>511300</v>
+      </c>
+      <c r="F52" s="3">
         <v>583600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>578700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>537600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>511400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>501300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>561600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>533800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>521700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>542600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>513600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>541100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>545200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>507000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1725700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2357000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2283500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2409200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2460200</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3411,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30521600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30279300</v>
+      </c>
+      <c r="F54" s="3">
         <v>29775200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29525100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29481400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28045400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28222700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>31619600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30391000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29703300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31041600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29385000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>29969400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>30194500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>30349400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>28892800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>29217200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>30144400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>28181100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>28931500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3505,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,362 +3530,400 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>864100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>857200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2483300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2462500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>732300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>696600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2401100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2690100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>984800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>962500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3231800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3059300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1058900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1066900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2692900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>716900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>650100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>665000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2996200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2931300</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2658800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3138300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3112000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3181700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3026700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2365200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2649900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2877600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2812500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1841900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1743600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2073200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2088800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3067400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2227400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2220100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2432400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1470300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>764300</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1865100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1850300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1244000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1233500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1825900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1736900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1109000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1242500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2001600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1956300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1224300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1158900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1908800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1923200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1396000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3466800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3771700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3559300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1854700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7189200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7132100</v>
+      </c>
+      <c r="F60" s="3">
         <v>7302600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7241200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7553300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7185400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6309200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7068600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7690200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7516100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6784600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6422500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6716800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6767300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7608900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6411100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6641900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6656700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6321200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5332600</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10411600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10328900</v>
+      </c>
+      <c r="F61" s="3">
         <v>9369700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9291000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8699900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8276200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>8771000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9826700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8617600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8422600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9388500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8887500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8491200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8555000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8156700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10074500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>10365500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>11010700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9946000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11333600</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>212800</v>
+      </c>
+      <c r="F62" s="3">
         <v>206800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>205000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>160600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>152800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>203600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>228100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>137400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>134300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>224300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>212300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>386700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>389600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>279300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2289400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2243100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2291500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2299400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2667300</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3981,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +4046,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +4111,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20154300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>19994200</v>
+      </c>
+      <c r="F66" s="3">
         <v>19276900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>19115000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18784500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17869500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>17551200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>19663700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18813700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18388000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>18963200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>17951200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18111800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>18247800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>18389200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19230800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>19693900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>20410800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>18554100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>19321000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4205,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4266,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4331,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4396,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4461,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8195100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8130000</v>
+      </c>
+      <c r="F72" s="3">
         <v>6577500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6522300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7750600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7373100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>6049300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>6777400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7832300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7655000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6868400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6501900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8115100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>8176100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>6726700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6713000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6594500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6796300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6684500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6675200</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4591,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4656,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4721,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8702900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8633800</v>
+      </c>
+      <c r="F76" s="3">
         <v>8892700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8818000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9112300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8668500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9168300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10271800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9956000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9730700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>10424000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9867700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>10254200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10331300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>10307900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9662000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9523200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>9733600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9627100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>9610500</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,72 +4851,84 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4581,23 +4971,29 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>731600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>447400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>753700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>609400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>815900</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,56 +5015,58 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>190800</v>
+      </c>
+      <c r="F83" s="3">
         <v>743200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>832700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>271900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>265700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>761100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>720500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>245600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>247400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>768000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>728000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>334200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>363900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>795800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -4678,8 +5076,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +5141,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5206,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5271,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5336,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5401,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1354900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1344100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1213000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1202800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1361000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1294700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>981500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1099600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1339700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1309400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1033700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>978600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1309800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1319700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>974000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2294100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2814300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1808400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2558100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1864000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5495,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-471100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-467400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-415900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-412400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-382900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-364200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-373500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-418400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-378000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-369400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-393700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-372700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-445900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-449300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-385400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1597000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1935000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1507000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-926400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1214200</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5621,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5686,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-601200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-596400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-578600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-573800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-486500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-462800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-583000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-653100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-931700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-910700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-748800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-708800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-594000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-598500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1415800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-517700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1160100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-802600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-942900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1449100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,67 +5780,75 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>408500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>405300</v>
+      </c>
+      <c r="F96" s="3">
         <v>360500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>357500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>359600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>342100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>321800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>360500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>346900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>339100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>334700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>316800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>442100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>445400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>215900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-633700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-626400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-629300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-629300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-865500</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5906,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5971,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +6036,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-862300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-855500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-485900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-481800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-868700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-826400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-416800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-467000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-399700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-390600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-253600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-240000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-754400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-760100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>441100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1223300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1808800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-919100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1574200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-469100</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F101" s="3">
         <v>11800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>6200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>6800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>5100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-22700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-114300</v>
+      </c>
+      <c r="F102" s="3">
         <v>141400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>140200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-7300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>9800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>28600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>27100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-36600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-36900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>530400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-156600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>88000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>41700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-52300</v>
       </c>
     </row>
